--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -492,16 +492,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -530,16 +522,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -568,16 +552,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -601,21 +577,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -644,16 +608,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -682,16 +638,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -720,16 +668,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -758,16 +698,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -796,16 +728,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -834,16 +758,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -867,21 +783,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -910,16 +814,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -948,16 +844,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -986,16 +874,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1024,16 +904,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1062,16 +934,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1100,16 +964,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1138,16 +994,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1176,16 +1024,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1209,21 +1049,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1247,21 +1075,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1285,21 +1101,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1323,21 +1127,9 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1352,7 +1144,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1361,21 +1153,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1390,7 +1170,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1399,21 +1179,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1428,7 +1196,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1437,21 +1205,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1466,7 +1222,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1475,21 +1231,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1504,7 +1248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1513,21 +1257,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1542,7 +1274,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1551,21 +1283,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1580,7 +1300,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1589,21 +1309,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1627,21 +1335,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1670,16 +1366,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1708,16 +1396,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1746,16 +1426,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1784,16 +1456,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1822,16 +1486,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1860,16 +1516,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1898,16 +1546,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1936,16 +1576,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1974,16 +1606,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2012,16 +1636,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2050,16 +1666,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2088,16 +1696,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2126,16 +1726,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2164,16 +1756,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2202,16 +1786,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2235,21 +1811,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2278,16 +1842,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2316,16 +1872,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2354,16 +1902,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2392,16 +1932,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2430,16 +1962,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2468,16 +1992,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2501,21 +2017,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2544,16 +2048,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2582,16 +2078,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2620,16 +2108,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2658,16 +2138,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2696,16 +2168,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2734,16 +2198,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2772,16 +2228,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2805,21 +2253,9 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,25 +478,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>ydh1184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -549,14 +549,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -568,21 +568,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4832961884</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -594,25 +598,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -624,18 +628,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -654,18 +658,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -684,18 +688,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -714,25 +718,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833576113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -744,25 +748,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832799612</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -774,7 +778,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -783,7 +787,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -800,18 +808,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -890,7 +898,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -908,7 +916,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -920,7 +928,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -931,7 +939,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -950,18 +958,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -980,18 +988,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1010,18 +1018,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1040,21 +1048,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kk_4832411690</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1078,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1092,21 +1108,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>kk_4832425669</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1138,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1127,7 +1147,11 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
@@ -1144,7 +1168,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>sjjeon1928</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1153,7 +1177,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
@@ -1170,7 +1198,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1179,12 +1207,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1228,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1205,12 +1237,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1258,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1231,12 +1267,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1288,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1257,7 +1297,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
@@ -1274,7 +1318,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1283,7 +1327,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
@@ -1300,7 +1348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1309,12 +1357,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1378,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1335,54 +1387,58 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4832411690</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1393,56 +1449,56 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1467,23 +1523,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1497,102 +1553,102 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4832556634</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1603,56 +1659,56 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>kk_4832269209</t>
+          <t>dave1102</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1663,26 +1719,26 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1693,56 +1749,56 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1753,26 +1809,26 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1783,82 +1839,86 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1869,26 +1929,26 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4832771015</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1899,232 +1959,236 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4833435690</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4833215714</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kk_4832269209</t>
+          <t>kk_4833692238</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833915167</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2135,128 +2199,2652 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>high_intent</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>kk_4832963009</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>kk_4832497383</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>kk_4833788564</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>hlpt10</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>kk_4832855902</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>kk_4832804456</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>kk_4832888908</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>mystyle1999</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>kk_4832527479</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>kk_4832745335</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>jinchoi24</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>kk_4832811973</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>kk_4833676329</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>kk_4833836842</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hotsnoopy</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>thdud9181</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>kk_4831402433</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>kk_4833961109</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>kk_4833294708</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>kk_4831784738</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>kk_4833706874</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>kk_4832310183</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>kk_4833232918</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>non_buyer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>pjj1758</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>kk_4831895164</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>kk_4831740520</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>kk_4830523585</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>kk_4833676515</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>kk_4832269209</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>kk_4833894015</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>kk_4833753902</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>kk_4833855255</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>kk_4833840470</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>kk_4832656308</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>kk_4832738942</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>kk_4833797203</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>kk_4833733292</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>lily50</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>kk_4833289287</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>kk_4832497383</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>kk_4832804456</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>mystyle1999</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>kk_4832745335</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cart_abandon</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>kk_4833676329</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>kk_4830885654</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>kk_4831895164</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>kk_4832593419</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>kk_4831740520</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>kk_4830523585</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>kk_4833676515</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>kk_4832659421</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>kk_4833493849</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>kk_4832269209</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>kk_4833894015</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>kk_4832293158</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>kk_4833753902</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>kk_4833855255</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>kk_4832162309</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>kk_4833840470</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>kk_4830212469</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>kk_4833715500</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>masterk</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>kk_4832656308</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>kk_4832738942</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>kk_4833682381</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>kk_4833797203</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>kk_4832648970</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>kk_4833733292</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>lily50</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>kk_4833698569</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>kk_4832345614</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>kk_4833435690</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>kk_4833692238</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>kk_4833289287</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>kk_4833588305</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>kk_4833858368</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>kk_4832963009</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>kk_4832497383</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>kk_4832855902</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>kk_4832804456</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>kk_4832888908</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>mystyle1999</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>kk_4832745335</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>kk_4833676329</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>high_intent</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>kk_4833836842</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
         </is>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kk_4833682381</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>whitehole147</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1306,7 +1306,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4833013784</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1336,7 +1336,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>arumabc</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kk_4833617385</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>kk_4833397488</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4833698569</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4833115356</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>kk_4832562814</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kk_4833867742</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kk_4832564458</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kk_4832735078</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4832986577</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wngml5609</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ckddbs4958</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kk_4833234218</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4832874454</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4833289287</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kk_4833858368</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kk_4833937502</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>hlpt10</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kk_4832855902</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -2506,7 +2506,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>mystyle1999</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>kk_4832527479</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kk_4832745335</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2596,7 +2596,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kk_4833961109</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kk_4833294708</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kk_4833706874</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>kk_4833232918</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pjj1758</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>kk_4833733292</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -4306,7 +4306,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>kk_4833733292</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>kk_4832804456</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -4726,7 +4726,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2523,12 +2523,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2538,25 +2538,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2566,35 +2566,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3789625265</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01029773942</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2607,22 +2607,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3789625265</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01029773942</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2719,12 +2719,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2734,13 +2734,13 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2818,13 +2818,13 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3139,12 +3139,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3167,40 +3167,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3223,96 +3223,96 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3363,22 +3363,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3391,12 +3391,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3419,28 +3419,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3475,40 +3475,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3518,25 +3518,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3546,25 +3546,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3574,25 +3574,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3615,22 +3615,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3643,12 +3643,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3658,35 +3658,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3699,12 +3699,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3714,63 +3714,63 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3783,40 +3783,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3826,25 +3826,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3867,12 +3867,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3882,35 +3882,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3923,22 +3923,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3951,22 +3951,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3979,12 +3979,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3994,25 +3994,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4022,25 +4022,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4063,22 +4063,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4091,50 +4091,50 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4147,22 +4147,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4175,40 +4175,40 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4218,53 +4218,53 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4285105163</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01083283220</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>endruns</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01020716852</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4274,35 +4274,35 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4315,22 +4315,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>kk_4285105163</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01083283220</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -4343,12 +4343,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4358,41 +4358,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4427,12 +4427,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4442,53 +4442,53 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4498,35 +4498,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>EDM_0224</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4539,12 +4539,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4554,35 +4554,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4595,40 +4595,40 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>endruns</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01020716852</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4638,35 +4638,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4679,22 +4679,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4707,12 +4707,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4735,40 +4735,40 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4778,53 +4778,53 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4834,63 +4834,63 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4903,12 +4903,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4918,35 +4918,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4959,40 +4959,40 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -5015,12 +5015,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5030,35 +5030,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5071,17 +5071,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5092,19 +5092,19 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5114,63 +5114,63 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EDM_0331</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>goppagi</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01052632529</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5183,12 +5183,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5198,35 +5198,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5239,22 +5239,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5267,40 +5267,40 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5323,73 +5323,73 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5400,47 +5400,47 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -5463,22 +5463,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -5491,12 +5491,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5506,25 +5506,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5534,53 +5534,53 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -5603,96 +5603,96 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>goppagi</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01052632529</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -5715,12 +5715,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5743,68 +5743,68 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5814,35 +5814,35 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5855,50 +5855,50 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5911,12 +5911,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5926,25 +5926,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>ko7417</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01041821439</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -5967,22 +5967,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -6023,68 +6023,68 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6094,25 +6094,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6135,50 +6135,50 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ko7417</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01041821439</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -6191,22 +6191,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -6219,22 +6219,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -6247,12 +6247,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6268,19 +6268,19 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6296,19 +6296,19 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6318,25 +6318,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6346,13 +6346,13 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -6387,40 +6387,40 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6430,35 +6430,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -6471,12 +6471,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6499,68 +6499,68 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6570,35 +6570,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6611,78 +6611,78 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6695,40 +6695,40 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6744,47 +6744,47 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6807,12 +6807,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6822,81 +6822,81 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>kk_3804201157</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01055152547</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6906,119 +6906,119 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -7031,78 +7031,78 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -7115,12 +7115,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -7143,22 +7143,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -7171,17 +7171,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7192,19 +7192,19 @@
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_3804201157</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01055152547</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7214,109 +7214,109 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7326,53 +7326,53 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7382,25 +7382,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7423,12 +7423,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7444,19 +7444,19 @@
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7466,25 +7466,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7507,50 +7507,50 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -7563,12 +7563,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -7591,12 +7591,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7606,53 +7606,53 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -7675,190 +7675,190 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -7871,96 +7871,96 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kiraeo</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01085072563</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7970,25 +7970,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7998,53 +7998,53 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kiraeo</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01085072563</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -8067,40 +8067,40 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -8123,22 +8123,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8151,68 +8151,68 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8222,25 +8222,25 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8263,12 +8263,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8284,19 +8284,19 @@
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8312,57 +8312,57 @@
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -8375,50 +8375,50 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -8431,12 +8431,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8459,22 +8459,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -8487,12 +8487,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8515,40 +8515,40 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8564,29 +8564,29 @@
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -8599,12 +8599,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -8627,12 +8627,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8642,81 +8642,81 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>kk_4840198421</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01053706365</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -8739,12 +8739,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -8767,40 +8767,40 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -8823,12 +8823,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -8851,12 +8851,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8879,22 +8879,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -8907,78 +8907,78 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -8991,22 +8991,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9019,22 +9019,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -9047,12 +9047,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9068,113 +9068,113 @@
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -9187,12 +9187,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9215,78 +9215,78 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
@@ -9299,12 +9299,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9327,40 +9327,40 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9376,19 +9376,19 @@
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9411,96 +9411,96 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9516,19 +9516,19 @@
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9544,29 +9544,29 @@
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -9579,12 +9579,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9594,25 +9594,25 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9622,25 +9622,25 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9656,19 +9656,19 @@
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9691,40 +9691,40 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -9747,96 +9747,96 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9846,25 +9846,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
@@ -9887,12 +9887,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9915,40 +9915,40 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -9958,25 +9958,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9986,25 +9986,25 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10027,78 +10027,78 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -10111,96 +10111,96 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_4840198421</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01053706365</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10210,25 +10210,25 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10251,50 +10251,50 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
@@ -10307,12 +10307,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10335,40 +10335,40 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -10391,12 +10391,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10412,187 +10412,187 @@
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
@@ -10615,12 +10615,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10636,47 +10636,47 @@
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -10699,12 +10699,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10727,12 +10727,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10742,35 +10742,35 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -10783,12 +10783,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10804,19 +10804,19 @@
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10839,12 +10839,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -10867,40 +10867,40 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10923,12 +10923,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -10951,12 +10951,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10979,22 +10979,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -11007,180 +11007,180 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11196,47 +11196,47 @@
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -11259,12 +11259,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11274,119 +11274,119 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11399,96 +11399,96 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11504,75 +11504,75 @@
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11588,57 +11588,57 @@
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -11651,12 +11651,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11672,19 +11672,19 @@
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11694,25 +11694,25 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11722,25 +11722,25 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -11763,12 +11763,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11784,19 +11784,19 @@
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11812,75 +11812,75 @@
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11896,29 +11896,29 @@
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -11931,40 +11931,40 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -11987,12 +11987,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2523,12 +2523,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2538,35 +2538,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2579,28 +2579,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2747,50 +2747,50 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2803,12 +2803,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2818,13 +2818,13 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2859,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2887,56 +2887,56 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4772822345</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01036338705</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>kk_4772822345</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01036338705</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2971,22 +2971,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>staylus11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01055097903</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2999,22 +2999,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>staylus11</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01055097903</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3055,12 +3055,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3083,22 +3083,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>astro77</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01091518663</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3111,12 +3111,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3139,96 +3139,96 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>astro77</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01091518663</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_3628696638_2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01038262132</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3238,53 +3238,53 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3307,12 +3307,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3335,22 +3335,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_3628696638_2</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01038262132</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3363,22 +3363,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3391,12 +3391,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3475,12 +3475,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3490,35 +3490,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3531,22 +3531,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3559,12 +3559,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3574,25 +3574,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3602,35 +3602,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3643,12 +3643,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3658,25 +3658,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3699,40 +3699,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3755,12 +3755,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3770,25 +3770,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3798,25 +3798,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3826,13 +3826,13 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3867,68 +3867,68 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3938,35 +3938,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4007,22 +4007,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -4063,78 +4063,78 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4147,78 +4147,78 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>endruns</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01020716852</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -4231,50 +4231,50 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>endruns</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01020716852</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -4287,22 +4287,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4343,96 +4343,96 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0224</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4614762502</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01064155845</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -4455,22 +4455,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4614762502</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01064155845</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4483,12 +4483,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4498,35 +4498,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4539,40 +4539,40 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4595,22 +4595,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4623,12 +4623,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4638,35 +4638,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4679,40 +4679,40 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4735,68 +4735,68 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4806,35 +4806,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4847,50 +4847,50 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4903,12 +4903,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4918,35 +4918,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4959,12 +4959,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4974,25 +4974,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0331</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5002,41 +5002,41 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5071,22 +5071,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5099,12 +5099,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5114,81 +5114,81 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>goppagi</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01052632529</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -5239,12 +5239,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5254,35 +5254,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5295,12 +5295,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5323,22 +5323,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5351,12 +5351,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5379,17 +5379,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5400,85 +5400,85 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -5491,12 +5491,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -5519,22 +5519,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -5547,78 +5547,78 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5631,22 +5631,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5659,40 +5659,40 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5702,81 +5702,81 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>sbstkd</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01084506080</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5799,17 +5799,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>goppagi</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01052632529</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5820,75 +5820,75 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5898,35 +5898,35 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5967,22 +5967,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5995,12 +5995,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>sbstkd</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01084506080</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6010,119 +6010,119 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -6135,12 +6135,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -6163,22 +6163,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -6191,22 +6191,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -6219,12 +6219,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6234,35 +6234,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -6275,78 +6275,78 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6359,50 +6359,50 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_4840238333</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01087443182</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -6415,22 +6415,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -6443,40 +6443,40 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6486,25 +6486,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6527,50 +6527,50 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -6583,12 +6583,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6598,25 +6598,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6626,91 +6626,91 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -6723,50 +6723,50 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -6779,22 +6779,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6807,22 +6807,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -6835,50 +6835,50 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -6919,12 +6919,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6940,29 +6940,29 @@
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -6975,40 +6975,40 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -7031,68 +7031,68 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7102,25 +7102,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7130,25 +7130,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7158,63 +7158,63 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>kk_4840238333</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01087443182</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7227,12 +7227,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7242,35 +7242,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7283,12 +7283,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7311,68 +7311,68 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7382,25 +7382,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kiraeo</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01085072563</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7410,81 +7410,81 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7507,68 +7507,68 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7578,81 +7578,81 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7668,75 +7668,75 @@
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7746,35 +7746,35 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -7787,12 +7787,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7802,25 +7802,25 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7830,35 +7830,35 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -7871,96 +7871,96 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7970,25 +7970,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -8011,40 +8011,40 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kiraeo</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01085072563</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -8067,12 +8067,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8082,13 +8082,13 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8123,40 +8123,40 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8166,25 +8166,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8200,75 +8200,75 @@
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8284,19 +8284,19 @@
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8319,12 +8319,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8340,159 +8340,159 @@
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8515,12 +8515,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -8543,12 +8543,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8564,19 +8564,19 @@
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8586,25 +8586,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8614,25 +8614,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8655,22 +8655,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -8683,12 +8683,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8711,12 +8711,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8726,25 +8726,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8760,19 +8760,19 @@
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8795,12 +8795,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8810,35 +8810,35 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -8851,12 +8851,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8872,19 +8872,19 @@
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8894,25 +8894,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8922,63 +8922,63 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -8991,68 +8991,68 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9068,19 +9068,19 @@
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9096,57 +9096,57 @@
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -9159,50 +9159,50 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9215,12 +9215,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9236,75 +9236,75 @@
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9314,63 +9314,63 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4840198421</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01053706365</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
@@ -9383,152 +9383,152 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9551,68 +9551,68 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9628,57 +9628,57 @@
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9691,68 +9691,68 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9762,81 +9762,81 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9846,63 +9846,63 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
@@ -9915,68 +9915,68 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9999,12 +9999,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10027,50 +10027,50 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
@@ -10083,12 +10083,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10098,35 +10098,35 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
@@ -10139,50 +10139,50 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>kk_4840198421</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01053706365</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -10195,12 +10195,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -10223,40 +10223,40 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
@@ -10279,12 +10279,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10307,12 +10307,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10328,29 +10328,29 @@
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -10363,12 +10363,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10384,19 +10384,19 @@
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10406,25 +10406,25 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -10447,40 +10447,40 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10496,147 +10496,147 @@
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10671,12 +10671,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10686,53 +10686,53 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -10755,12 +10755,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10776,19 +10776,19 @@
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10804,19 +10804,19 @@
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10826,53 +10826,53 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -10895,40 +10895,40 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -10951,12 +10951,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10979,22 +10979,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -11007,12 +11007,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11028,57 +11028,57 @@
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -11091,12 +11091,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11112,29 +11112,29 @@
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -11147,40 +11147,40 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11196,47 +11196,47 @@
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11259,78 +11259,78 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -11343,129 +11343,129 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -11476,19 +11476,19 @@
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11511,68 +11511,68 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11595,68 +11595,68 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11672,19 +11672,19 @@
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11700,19 +11700,19 @@
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11722,53 +11722,53 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11784,75 +11784,75 @@
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -11875,12 +11875,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11896,29 +11896,29 @@
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -11931,68 +11931,68 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12002,13 +12002,13 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2551,56 +2551,56 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_3178599665</t>
+          <t>kk_3500501777</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01089430429</t>
+          <t>01038347573</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2663,22 +2663,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3500501777</t>
+          <t>kk_3178599665</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01038347573</t>
+          <t>01089430429</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2719,12 +2719,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2734,25 +2734,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2762,35 +2762,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2803,22 +2803,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2859,12 +2859,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2887,68 +2887,68 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_4772822345</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01036338705</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4772822345</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01036338705</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>justicek73</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01033270931</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2971,22 +2971,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>staylus11</t>
+          <t>justicek73</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01055097903</t>
+          <t>01033270931</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2999,12 +2999,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3014,41 +3014,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>staylus11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01055097903</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3083,12 +3083,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3139,12 +3139,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>astro77</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01091518663</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3167,56 +3167,56 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3251,40 +3251,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3307,12 +3307,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3335,12 +3335,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3363,22 +3363,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3391,12 +3391,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3406,63 +3406,63 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>astro77</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01091518663</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3475,50 +3475,50 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3531,22 +3531,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3559,68 +3559,68 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3643,22 +3643,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3671,12 +3671,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3686,81 +3686,81 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3770,53 +3770,53 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3839,22 +3839,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3867,106 +3867,106 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3979,190 +3979,190 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4203,12 +4203,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0224</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -4231,12 +4231,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4259,50 +4259,50 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4315,68 +4315,68 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4285105163</t>
+          <t>kk_4614762502</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01083283220</t>
+          <t>01064155845</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4399,12 +4399,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4414,81 +4414,81 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4614762502</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01064155845</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4498,25 +4498,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4539,50 +4539,50 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4595,22 +4595,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_4285105163</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01083283220</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4623,40 +4623,40 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4666,25 +4666,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4694,25 +4694,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4722,63 +4722,63 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4791,22 +4791,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4819,12 +4819,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4834,35 +4834,35 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -4875,12 +4875,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4903,12 +4903,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4931,40 +4931,40 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>sbstkd</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01084506080</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4974,25 +4974,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5002,53 +5002,53 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5071,106 +5071,106 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5183,12 +5183,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>ko7417</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01041821439</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -5211,22 +5211,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5239,12 +5239,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5254,35 +5254,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5295,12 +5295,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5323,12 +5323,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5351,40 +5351,40 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5407,12 +5407,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5422,25 +5422,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0331</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5450,53 +5450,53 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5519,12 +5519,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -5547,22 +5547,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>goppagi</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01052632529</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -5575,12 +5575,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5590,25 +5590,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5631,22 +5631,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5659,12 +5659,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5680,85 +5680,85 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>sbstkd</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01084506080</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5771,45 +5771,45 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>goppagi</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01052632529</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5820,47 +5820,47 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5870,63 +5870,63 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5939,50 +5939,50 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ko7417</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01041821439</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5995,40 +5995,40 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6038,35 +6038,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6079,22 +6079,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -6107,12 +6107,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6122,63 +6122,63 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -6191,22 +6191,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -6219,12 +6219,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6234,53 +6234,53 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6290,91 +6290,91 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -6387,12 +6387,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6430,81 +6430,81 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6527,162 +6527,162 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6695,68 +6695,68 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6766,53 +6766,53 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>kk_3804201157</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01055152547</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6822,63 +6822,63 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -6891,106 +6891,106 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_3804201157</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01055152547</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -7003,40 +7003,40 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kk_4840238333</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01087443182</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7046,63 +7046,63 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -7115,12 +7115,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7130,25 +7130,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7158,13 +7158,13 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_4840238333</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01087443182</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7227,12 +7227,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7242,63 +7242,63 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7311,12 +7311,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7326,53 +7326,53 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7382,13 +7382,13 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -7423,22 +7423,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7451,22 +7451,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7479,45 +7479,45 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7528,19 +7528,19 @@
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -7563,96 +7563,96 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7662,25 +7662,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7690,25 +7690,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7718,53 +7718,53 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7774,53 +7774,53 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7836,47 +7836,47 @@
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7886,25 +7886,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7914,25 +7914,25 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7942,25 +7942,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7970,25 +7970,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7998,25 +7998,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8026,25 +8026,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8054,25 +8054,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8082,25 +8082,25 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -8123,68 +8123,68 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8194,81 +8194,81 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8284,19 +8284,19 @@
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8312,19 +8312,19 @@
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8334,53 +8334,53 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -8403,96 +8403,96 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8508,57 +8508,57 @@
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -8571,40 +8571,40 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8620,57 +8620,57 @@
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -8683,40 +8683,40 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8739,12 +8739,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8760,29 +8760,29 @@
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8795,12 +8795,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -8823,40 +8823,40 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8866,25 +8866,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8894,25 +8894,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
@@ -8935,12 +8935,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8956,57 +8956,57 @@
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9019,40 +9019,40 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9068,85 +9068,85 @@
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -9159,12 +9159,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -9174,53 +9174,53 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9230,81 +9230,81 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9314,13 +9314,13 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9355,12 +9355,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9376,47 +9376,47 @@
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9432,19 +9432,19 @@
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9460,19 +9460,19 @@
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9482,53 +9482,53 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9544,29 +9544,29 @@
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -9579,124 +9579,124 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9712,47 +9712,47 @@
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9762,91 +9762,91 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
@@ -9859,50 +9859,50 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
@@ -9915,12 +9915,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9943,12 +9943,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -9958,109 +9958,109 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10076,85 +10076,85 @@
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
@@ -10167,12 +10167,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10195,12 +10195,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10210,81 +10210,81 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10307,12 +10307,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10335,22 +10335,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -10363,12 +10363,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10391,12 +10391,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10406,25 +10406,25 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -10447,50 +10447,50 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -10503,106 +10503,106 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
@@ -10615,22 +10615,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -10643,40 +10643,40 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10692,47 +10692,47 @@
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10742,25 +10742,25 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10776,19 +10776,19 @@
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10804,19 +10804,19 @@
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -10839,12 +10839,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10860,7 +10860,7 @@
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -10895,22 +10895,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -10923,12 +10923,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10951,12 +10951,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10972,19 +10972,19 @@
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11000,19 +11000,19 @@
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11022,25 +11022,25 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11063,68 +11063,68 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11134,25 +11134,25 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11168,19 +11168,19 @@
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11203,12 +11203,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11224,19 +11224,19 @@
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11259,40 +11259,40 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11302,63 +11302,63 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11371,12 +11371,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11399,68 +11399,68 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11470,25 +11470,25 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11504,57 +11504,57 @@
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -11567,12 +11567,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11595,22 +11595,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -11623,12 +11623,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11651,12 +11651,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11672,19 +11672,19 @@
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11694,81 +11694,81 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11791,12 +11791,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -11819,68 +11819,68 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11896,103 +11896,103 @@
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12002,13 +12002,13 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2523,12 +2523,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2538,25 +2538,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2566,35 +2566,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3789625265</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01029773942</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2607,22 +2607,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3789625265</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01029773942</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2719,28 +2719,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2803,28 +2803,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2859,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2915,12 +2915,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2943,12 +2943,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>justicek73</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01033270931</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2971,12 +2971,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>justicek73</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01033270931</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2992,19 +2992,19 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3014,13 +3014,13 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3055,40 +3055,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3111,12 +3111,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3126,53 +3126,53 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3182,25 +3182,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3223,22 +3223,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_3628696638_2</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01038262132</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3251,12 +3251,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3279,40 +3279,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>astro77</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01091518663</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3335,22 +3335,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_3628696638_2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01038262132</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3363,12 +3363,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3378,25 +3378,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3406,53 +3406,53 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>astro77</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01091518663</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3475,50 +3475,50 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3531,22 +3531,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3559,12 +3559,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3574,25 +3574,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3615,12 +3615,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3643,22 +3643,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3671,106 +3671,106 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3783,50 +3783,50 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3839,40 +3839,40 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3882,109 +3882,109 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3994,81 +3994,81 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4091,40 +4091,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>kk_4285105163</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01083283220</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4147,22 +4147,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>endruns</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01020716852</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4175,50 +4175,50 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>endruns</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01020716852</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -4231,12 +4231,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4315,12 +4315,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4614762502</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01064155845</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4343,40 +4343,40 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4386,25 +4386,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4414,35 +4414,35 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -4455,12 +4455,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4483,12 +4483,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4511,106 +4511,106 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4285105163</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01083283220</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4623,22 +4623,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4651,12 +4651,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4666,35 +4666,35 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0224</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4707,12 +4707,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4735,40 +4735,40 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4791,22 +4791,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4819,22 +4819,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_4614762502</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01064155845</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4847,40 +4847,40 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4903,106 +4903,106 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sbstkd</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01084506080</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -5015,12 +5015,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -5043,12 +5043,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5071,22 +5071,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5099,68 +5099,68 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5170,63 +5170,63 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ko7417</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01041821439</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5239,28 +5239,28 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5323,22 +5323,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5351,40 +5351,40 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5394,58 +5394,58 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5463,40 +5463,40 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5506,35 +5506,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -5603,12 +5603,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5618,25 +5618,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5659,96 +5659,96 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>sbstkd</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01084506080</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5771,68 +5771,68 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5855,84 +5855,84 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0331</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5995,68 +5995,68 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6079,12 +6079,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -6107,22 +6107,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -6135,12 +6135,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -6163,40 +6163,40 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>ko7417</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01041821439</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -6219,68 +6219,68 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6290,53 +6290,53 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6359,12 +6359,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -6387,96 +6387,96 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6486,25 +6486,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6527,22 +6527,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -6555,22 +6555,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -6583,12 +6583,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6598,25 +6598,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6626,25 +6626,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -6667,40 +6667,40 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -6723,40 +6723,40 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6766,25 +6766,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_3804201157</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01055152547</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6807,12 +6807,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -6835,12 +6835,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -6863,180 +6863,180 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kk_4840238333</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01087443182</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7046,25 +7046,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7074,35 +7074,35 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_3804201157</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01055152547</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -7115,40 +7115,40 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7158,25 +7158,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -7199,78 +7199,78 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7283,12 +7283,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7311,40 +7311,40 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7354,63 +7354,63 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kiraeo</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01085072563</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7423,12 +7423,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7451,22 +7451,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7479,12 +7479,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_4840238333</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01087443182</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7507,22 +7507,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>kiraeo</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01085072563</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -7535,12 +7535,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7550,53 +7550,53 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -7619,68 +7619,68 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -7703,12 +7703,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7718,53 +7718,53 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7774,53 +7774,53 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -7843,40 +7843,40 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7886,25 +7886,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -7983,12 +7983,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7998,53 +7998,53 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -8067,12 +8067,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8082,63 +8082,63 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8151,96 +8151,96 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8256,19 +8256,19 @@
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8284,47 +8284,47 @@
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8334,109 +8334,109 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8459,12 +8459,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8480,85 +8480,85 @@
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8599,12 +8599,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8614,53 +8614,53 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -8683,40 +8683,40 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8726,25 +8726,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8767,22 +8767,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8795,22 +8795,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -8823,40 +8823,40 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8866,35 +8866,35 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -8907,50 +8907,50 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -8963,22 +8963,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -8991,22 +8991,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9019,12 +9019,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -9047,12 +9047,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9068,75 +9068,75 @@
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>kk_4840198421</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01053706365</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9159,40 +9159,40 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9215,12 +9215,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9230,25 +9230,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9271,12 +9271,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
@@ -9299,12 +9299,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9320,85 +9320,85 @@
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_4840198421</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01053706365</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
@@ -9411,124 +9411,124 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -9551,12 +9551,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -9579,12 +9579,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9635,162 +9635,162 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
@@ -9803,40 +9803,40 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9852,19 +9852,19 @@
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9874,53 +9874,53 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9930,41 +9930,41 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
@@ -9999,40 +9999,40 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10042,91 +10042,91 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
@@ -10139,12 +10139,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10154,25 +10154,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10188,19 +10188,19 @@
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10210,35 +10210,35 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
@@ -10251,40 +10251,40 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10300,19 +10300,19 @@
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10335,22 +10335,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -10363,68 +10363,68 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -10447,40 +10447,40 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10496,19 +10496,19 @@
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -10518,53 +10518,53 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10574,25 +10574,25 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10615,40 +10615,40 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10671,96 +10671,96 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10776,19 +10776,19 @@
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10811,12 +10811,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10832,47 +10832,47 @@
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -10895,12 +10895,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10923,40 +10923,40 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10966,53 +10966,53 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11022,25 +11022,25 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11063,12 +11063,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11084,47 +11084,47 @@
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11147,12 +11147,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11168,47 +11168,47 @@
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11224,19 +11224,19 @@
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11259,22 +11259,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -11287,22 +11287,22 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -11315,50 +11315,50 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11371,50 +11371,50 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -11427,68 +11427,68 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11504,19 +11504,19 @@
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11526,35 +11526,35 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -11567,12 +11567,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11582,53 +11582,53 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -11651,12 +11651,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11672,19 +11672,19 @@
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
@@ -11707,12 +11707,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11722,53 +11722,53 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11784,103 +11784,103 @@
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11896,29 +11896,29 @@
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -11931,68 +11931,68 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12002,13 +12002,13 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,7 +569,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>veritaskm</t>
+          <t>kk_2905067716</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01084555847</t>
+          <t>01099172715</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EDM_0220</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,91 +623,91 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_2905067716</t>
+          <t>kk_4840543810</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01099172715</t>
+          <t>01076561839</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>THRIVE™ REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>przemysl</t>
+          <t>kk_4201213646</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01031646842</t>
+          <t>01027969918</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_ECOM_cart_sale</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HAZY JOURNEY™ II WATERPROOF</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4339471474</t>
+          <t>kk_4837269061</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01037475394</t>
+          <t>01071602672</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>KONOS SPEED TRAIL ATR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,27 +719,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bia5408</t>
+          <t>przemysl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01037225787</t>
+          <t>01031646842</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
+          <t>HAZY JOURNEY™ II WATERPROOF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -751,27 +751,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4546862086</t>
+          <t>kk_4339471474</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01067901783</t>
+          <t>01037475394</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Convertible Pant</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -783,12 +783,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4201213646</t>
+          <t>kk_3632271089</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01027969918</t>
+          <t>01035264297</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EDM_ECOM_cart_sale</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cove Beach Pant</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -815,27 +815,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shyguy0105</t>
+          <t>bia5408</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01038050293</t>
+          <t>01037225787</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,27 +847,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4823936009</t>
+          <t>kk_4546862086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01089393759</t>
+          <t>01067901783</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>Silver Ridge Elite Convertible Pant</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_4581508260</t>
+          <t>shyguy0105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01089654012</t>
+          <t>01038050293</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,27 +911,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jjjino</t>
+          <t>kk_4823936009</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01053807866</t>
+          <t>01089393759</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tumu Heights™ Jacket</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>firstbaek</t>
+          <t>sunnyway21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01042145317</t>
+          <t>01021890517</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>Triple Canyon 24L Backpack</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -975,27 +975,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>siwago</t>
+          <t>kk_4581508260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01033066627</t>
+          <t>01089654012</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>my8532185</t>
+          <t>jjjino</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01029602185</t>
+          <t>01053807866</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>W's Hollowtop Mountain 2L Jacket</t>
+          <t>Tumu Heights™ Jacket</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zzzing2sj</t>
+          <t>firstbaek</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01040825103</t>
+          <t>01042145317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JAAWAA WP</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,27 +1071,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>senggun</t>
+          <t>siwago</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01053217050</t>
+          <t>01033066627</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Silver Ridge Utility Vest</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,12 +1103,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_2958892604</t>
+          <t>my8532185</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01032407670</t>
+          <t>01029602185</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>W's Hollowtop Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,27 +1135,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4229942652</t>
+          <t>zzzing2sj</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01074586556</t>
+          <t>01040825103</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>M's Dart Forest Corduroy Shirts</t>
+          <t>JAAWAA WP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,27 +1167,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_3944538221</t>
+          <t>senggun</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01067575525</t>
+          <t>01053217050</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Light Canyon Soft Shell Jacket</t>
+          <t>Silver Ridge Utility Vest</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,27 +1199,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rkdwjd1107</t>
+          <t>umbro98sc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01086634156</t>
+          <t>01027941141</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4653279631</t>
+          <t>kk_2958892604</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01048492743</t>
+          <t>01032407670</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M's Jerry Cove Crew</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwertlhy</t>
+          <t>kk_4229942652</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01022573817</t>
+          <t>01074586556</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>THRIVE REVIVE SHANDAL</t>
+          <t>M's Dart Forest Corduroy Shirts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,27 +1295,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yalrud</t>
+          <t>rkdwjd1107</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01093710427</t>
+          <t>01086634156</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VOYAGER FLX PCT</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,27 +1327,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4742727612</t>
+          <t>kk_4653279631</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01048438355</t>
+          <t>01048492743</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pepper Rock 23L Backpack</t>
+          <t>M's Jerry Cove Crew</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4811115248</t>
+          <t>qwertlhy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01032638676</t>
+          <t>01022573817</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>M's Second Peak Crew</t>
+          <t>THRIVE REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4840268400</t>
+          <t>kk_4824047142</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01095248011</t>
+          <t>01093696318</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Castle Rock™ 25L Backpack II</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,27 +1423,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hikehiking</t>
+          <t>henhaojin</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01064558877</t>
+          <t>01053508016</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRESTWOOD MID WATERPROOF WIDE</t>
+          <t>M's Current Cove Tapered Pants</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,27 +1455,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4305828924</t>
+          <t>yalrud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01052248580</t>
+          <t>01093710427</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Castle Rock™ 20L Backpack II</t>
+          <t>VOYAGER FLX PCT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,12 +1487,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gamja</t>
+          <t>kk_4742727612</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01076747777</t>
+          <t>01048438355</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>Pepper Rock 23L Backpack</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,27 +1519,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4234884689_2</t>
+          <t>kk_4811115248</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01056418131</t>
+          <t>01032638676</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Marble Canyon™ Overlay Hoodie</t>
+          <t>M's Second Peak Crew</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>saramimda</t>
+          <t>hikehiking</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01072663960</t>
+          <t>01064558877</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MONTRAIL TRINITY AG II</t>
+          <t>CRESTWOOD MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4640153364</t>
+          <t>serejohn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01082254246</t>
+          <t>01062169182</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PFG Unted™ Pant</t>
+          <t>[GRAFFLEX] Dash to Cove Graphic Tee</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_3225225310</t>
+          <t>kk_4305828924</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01032977623</t>
+          <t>01052248580</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Castle Rock™ 20L Backpack II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,27 +1647,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>gamja</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01029767391</t>
+          <t>01076747777</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bonre Forest 20L Packable Backpack</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4304355753</t>
+          <t>kk_4234884689_2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01041289534</t>
+          <t>01056418131</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crest To Valley Graphic Ss Tee</t>
+          <t>Marble Canyon™ Overlay Hoodie</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iama99</t>
+          <t>kk_4640153364</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01085853044</t>
+          <t>01082254246</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Speed Trail Ball Cap</t>
+          <t>PFG Unted™ Pant</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ounorman</t>
+          <t>kk_3225225310</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01051592511</t>
+          <t>01032977623</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>boribori123</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01033660769</t>
+          <t>01029767391</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>Bonre Forest 20L Packable Backpack</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>c300047</t>
+          <t>kk_4304355753</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01032881635</t>
+          <t>01041289534</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Acker Rock Twill Short</t>
+          <t>Crest To Valley Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1871,40 +1871,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>jhoh55555</t>
+          <t>montrail</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01062626688</t>
+          <t>01096613534</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PFG Unted™ Pant</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4512211992</t>
+          <t>ounorman</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01040855407</t>
+          <t>01051592511</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,53 +1918,61 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Lake To Avenue Graphic Ss Tee</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>wooyes</t>
+          <t>boribori123</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01093487391</t>
+          <t>01033660769</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>c300047</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01032881635</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1970,25 +1982,29 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>KAKAO_CH_event</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Acker Rock Twill Short</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>c100224</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01053261660</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1998,63 +2014,67 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>W Saudan Pro 3L Shell</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3649011176</t>
+          <t>jhoh55555</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01029317964</t>
+          <t>01062626688</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_4512211992</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01040855407</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2067,12 +2087,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>lscbo76</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01025029158</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2082,7 +2102,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2095,12 +2115,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2110,7 +2130,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2123,12 +2143,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_3649011176</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01029317964</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2138,25 +2158,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2166,7 +2186,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2179,22 +2199,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2207,50 +2227,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>lscbo76</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01025029158</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2263,50 +2283,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>somsea</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01028811570</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>goril04624</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01047651746</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2319,22 +2339,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01098876431</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2347,50 +2367,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>mezzo304</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01032400300</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>somsea</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01028811570</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2403,22 +2423,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>mezzo304</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01032400300</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2431,22 +2451,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2459,22 +2479,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2487,22 +2507,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>zollee77</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01064740702</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2515,50 +2535,50 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2571,12 +2591,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2586,7 +2606,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2599,22 +2619,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2627,12 +2647,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2642,7 +2662,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2655,12 +2675,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2670,13 +2690,13 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2711,40 +2731,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2754,25 +2774,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2782,25 +2802,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4822475920</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01073932582</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2823,22 +2843,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2851,12 +2871,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2866,53 +2886,53 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2922,7 +2942,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2935,22 +2955,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2991,12 +3011,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4839289649</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01041713878</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3019,12 +3039,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3034,7 +3054,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3047,22 +3067,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3075,12 +3095,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3090,25 +3110,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3118,7 +3138,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3131,12 +3151,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3146,25 +3166,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3174,25 +3194,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3215,40 +3235,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3258,7 +3278,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3271,22 +3291,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3299,12 +3319,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3314,35 +3334,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3355,40 +3375,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3398,81 +3418,81 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4750697279</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01086127388</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3482,35 +3502,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3523,50 +3543,50 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3579,12 +3599,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>wjhj1400</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01064023952</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3594,25 +3614,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3622,7 +3642,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3635,22 +3655,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4326567662</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01046049921</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3663,22 +3683,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4836613952</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01041344927</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3691,17 +3711,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3712,29 +3732,29 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3747,106 +3767,106 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3859,22 +3879,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4836691459</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01072445075</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3887,106 +3907,106 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3999,50 +4019,50 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4055,17 +4075,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4076,75 +4096,75 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4167,68 +4187,68 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4238,7 +4258,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4251,78 +4271,78 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4840292707</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01085257253</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4335,40 +4355,40 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4485686054</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01030613096</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4378,63 +4398,63 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>hw00185</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01032596566</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4475,50 +4495,50 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4531,22 +4551,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4559,78 +4579,78 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4643,22 +4663,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4671,162 +4691,162 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4839,22 +4859,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4439122782</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01028252500</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4867,12 +4887,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4882,35 +4902,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4923,50 +4943,50 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4979,12 +4999,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5000,19 +5020,19 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5022,25 +5042,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5050,147 +5070,147 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5203,56 +5223,56 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
@@ -5287,124 +5307,124 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5420,169 +5440,169 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5595,28 +5615,28 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5653,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -5651,124 +5671,124 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5791,12 +5811,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5812,29 +5832,29 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5847,22 +5867,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5875,28 +5895,756 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
+          <t>FIRST_PURCHASE_COUPON</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>kk_2961062530</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>01050052823</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>kk_4841572668</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>01024164342</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>jyyon101</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>01050119990</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
           <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>nhs1024</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>01035177054</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>kk_2750710108</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>01062707475</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>kk_3858585698</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>01092163429</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>dpfmxkdl</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>01023221625</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Email_mkt</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>manong0821</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>01036923281</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>nikemkr</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>01032361592</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>kk_4351409443</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>01050585646</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>kk_4841140461</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>01088944649</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>FIRST_PURCHASE_COUPON</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>kk_3799202460</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>01051162376</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>kk_3152552457</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>01031327516</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>kk_4840669442</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>01093940957</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>jsb0425</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>01037883670</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>kk_3837527580</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>01084311738</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>poketgyu</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>01085474650</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>kk_4427490834</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>01034704205</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>jyseoul</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>01054813799</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>kk_4840846776</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>01055961435</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>mwnew5</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>01091343604</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>kk_4703272205</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>01062682325</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>hisgogo</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>01054110956</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>HIGH_INTENT_NUDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>nesto1</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>01056603953</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>kk_4840872605</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>01063782216</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>CART_REMINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>kyoungs424</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>01041509204</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F215"/>
+  <dimension ref="A1:F214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2087,22 +2087,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2115,22 +2115,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2255,12 +2255,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2283,50 +2283,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2339,50 +2339,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2479,12 +2479,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2507,22 +2507,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2535,22 +2535,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2563,22 +2563,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2591,12 +2591,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2619,22 +2619,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2647,12 +2647,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2662,25 +2662,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2703,28 +2703,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2759,50 +2759,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2843,12 +2843,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2871,12 +2871,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2886,25 +2886,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2955,22 +2955,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2983,50 +2983,50 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3039,12 +3039,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3054,35 +3054,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3095,12 +3095,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3123,12 +3123,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3138,53 +3138,53 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3194,35 +3194,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3235,40 +3235,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3291,22 +3291,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3319,12 +3319,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3347,22 +3347,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3375,28 +3375,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3474,53 +3474,53 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3530,25 +3530,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3558,25 +3558,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3586,35 +3586,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3627,22 +3627,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3655,22 +3655,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3711,12 +3711,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3726,35 +3726,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3795,12 +3795,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3810,86 +3810,86 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3907,40 +3907,40 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4840510971</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01083115500</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3950,35 +3950,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3991,40 +3991,40 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4034,25 +4034,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4062,25 +4062,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4090,63 +4090,63 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4159,12 +4159,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4215,40 +4215,40 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4258,25 +4258,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4299,50 +4299,50 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4355,12 +4355,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4370,81 +4370,81 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4454,53 +4454,53 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4510,25 +4510,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4551,22 +4551,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4579,50 +4579,50 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4635,12 +4635,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4650,35 +4650,35 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4691,162 +4691,162 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4859,40 +4859,40 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4902,53 +4902,53 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4958,35 +4958,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4999,40 +4999,40 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5042,137 +5042,137 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5182,35 +5182,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5223,78 +5223,78 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5307,12 +5307,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5335,12 +5335,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5350,63 +5350,63 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -5419,22 +5419,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -5447,12 +5447,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5462,35 +5462,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -5503,12 +5503,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5518,35 +5518,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -5559,22 +5559,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5587,96 +5587,96 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4841861142</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01052528559</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5727,12 +5727,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5742,137 +5742,137 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5882,25 +5882,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5923,22 +5923,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5951,106 +5951,106 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -6063,12 +6063,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6078,81 +6078,81 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6162,53 +6162,53 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4351409443</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01050585646</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6231,106 +6231,106 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -6343,12 +6343,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6364,19 +6364,19 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -6399,40 +6399,40 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>jyseoul</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01054813799</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6442,53 +6442,53 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6498,25 +6498,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6526,35 +6526,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6567,40 +6567,40 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6610,41 +6610,13 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>kyoungs424</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>01041509204</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2199,12 +2199,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>lscbo76</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01025029158</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2227,12 +2227,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lscbo76</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01025029158</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2255,50 +2255,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2311,40 +2311,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2354,41 +2354,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2423,22 +2423,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>mezzo304</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01032400300</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2451,22 +2451,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>mezzo304</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01032400300</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2479,22 +2479,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2507,22 +2507,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2563,22 +2563,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2619,12 +2619,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2647,40 +2647,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2690,53 +2690,53 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2746,25 +2746,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2774,81 +2774,81 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2858,25 +2858,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2899,12 +2899,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2927,40 +2927,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2983,68 +2983,68 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3054,35 +3054,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3095,12 +3095,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3110,35 +3110,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3151,22 +3151,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3179,22 +3179,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3207,22 +3207,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3263,12 +3263,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3284,29 +3284,29 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3319,12 +3319,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3334,53 +3334,53 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3390,53 +3390,53 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3446,35 +3446,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3487,22 +3487,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3515,12 +3515,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3530,25 +3530,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3571,68 +3571,68 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3642,63 +3642,63 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3711,22 +3711,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3739,17 +3739,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3767,68 +3767,68 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3838,63 +3838,63 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3907,22 +3907,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3935,78 +3935,78 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4019,12 +4019,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4047,12 +4047,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4075,78 +4075,78 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4159,50 +4159,50 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4215,22 +4215,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -4243,208 +4243,208 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4840510971</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01083115500</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4454,25 +4454,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4482,63 +4482,63 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4551,22 +4551,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4579,78 +4579,78 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4663,12 +4663,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4691,68 +4691,68 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4762,25 +4762,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4796,113 +4796,113 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4915,22 +4915,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4943,12 +4943,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4971,12 +4971,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4986,175 +4986,175 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -5167,12 +5167,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5182,25 +5182,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5210,13 +5210,13 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5251,22 +5251,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5279,40 +5279,40 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5322,25 +5322,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5350,35 +5350,35 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -5391,40 +5391,40 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5434,25 +5434,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5462,25 +5462,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -5503,124 +5503,124 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4841861142</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01052528559</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5643,12 +5643,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5658,25 +5658,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5686,35 +5686,35 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>acp1011</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01045809723</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5727,12 +5727,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5748,57 +5748,57 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5811,12 +5811,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5839,40 +5839,40 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5882,63 +5882,63 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5951,12 +5951,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5979,22 +5979,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6007,348 +6007,348 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_4351409443</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01050585646</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6358,35 +6358,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -6399,50 +6399,50 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6455,12 +6455,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6483,12 +6483,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6498,25 +6498,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -6539,22 +6539,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6567,12 +6567,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6595,22 +6595,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2143,56 +2143,56 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_3649011176</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01029317964</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_3649011176</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01029317964</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2270,35 +2270,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2311,84 +2311,84 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2479,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2507,12 +2507,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2535,22 +2535,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2563,22 +2563,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2591,12 +2591,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2606,25 +2606,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2647,22 +2647,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2675,22 +2675,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2703,22 +2703,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2731,12 +2731,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2746,13 +2746,13 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2802,63 +2802,63 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2871,12 +2871,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2886,35 +2886,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2927,12 +2927,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2955,40 +2955,40 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2998,25 +2998,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3026,25 +3026,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3067,12 +3067,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3095,12 +3095,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3123,40 +3123,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3179,12 +3179,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3194,63 +3194,63 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3263,12 +3263,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3278,35 +3278,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3319,40 +3319,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3375,22 +3375,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3403,22 +3403,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3431,22 +3431,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3459,12 +3459,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3474,35 +3474,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3515,96 +3515,96 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3614,13 +3614,13 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3655,68 +3655,68 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3739,17 +3739,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3767,12 +3767,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3782,53 +3782,53 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3851,50 +3851,50 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3907,106 +3907,106 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4019,17 +4019,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4047,40 +4047,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4090,25 +4090,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4131,68 +4131,68 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4202,86 +4202,86 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4327,96 +4327,96 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4426,91 +4426,91 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -4523,22 +4523,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4551,50 +4551,50 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4607,12 +4607,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4622,63 +4622,63 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4691,22 +4691,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4719,12 +4719,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4734,35 +4734,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4775,96 +4775,96 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4351409443</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01050585646</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4874,53 +4874,53 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4943,12 +4943,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4958,25 +4958,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4999,40 +4999,40 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5042,35 +5042,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5083,152 +5083,152 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4841861142</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01052528559</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5238,91 +5238,91 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5335,124 +5335,124 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5462,25 +5462,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5490,53 +5490,53 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5546,25 +5546,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5574,35 +5574,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5615,22 +5615,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -5643,134 +5643,134 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>acp1011</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01045809723</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5783,40 +5783,40 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5832,75 +5832,75 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5910,25 +5910,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5938,25 +5938,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5966,35 +5966,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6007,12 +6007,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6035,50 +6035,50 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -6091,22 +6091,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -6147,22 +6147,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -6203,22 +6203,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -6231,78 +6231,78 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6315,40 +6315,40 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6358,35 +6358,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -6399,22 +6399,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -6427,22 +6427,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6455,40 +6455,40 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6498,25 +6498,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6532,19 +6532,19 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6567,56 +6567,56 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F214"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kk_4369019019</t>
+          <t>kyj1084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01089068719</t>
+          <t>01087521084</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>M's Columbia Rock Down Jacket</t>
+          <t>PEAKFREAK RUSH™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,44 +527,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kyj1084</t>
+          <t>kk_3765311201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01087521084</t>
+          <t>01088512457</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH™ OUTDRY™ WIDE</t>
+          <t>W's Anne Road Down Jacket</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_3765311201</t>
+          <t>kk_2905067716</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01088512457</t>
+          <t>01099172715</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>W's Anne Road Down Jacket</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,76 +591,76 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_2905067716</t>
+          <t>kk_4840543810</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01099172715</t>
+          <t>01076561839</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>THRIVE™ REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4840543810</t>
+          <t>kk_4201213646</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01076561839</t>
+          <t>01027969918</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EDM_ECOM_cart_sale</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>THRIVE™ REVIVE SHANDAL</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4201213646</t>
+          <t>kk_4837269061</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01027969918</t>
+          <t>01071602672</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -670,44 +670,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EDM_ECOM_cart_sale</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cove Beach Pant</t>
+          <t>KONOS SPEED TRAIL ATR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4837269061</t>
+          <t>przemysl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01071602672</t>
+          <t>01031646842</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KONOS SPEED TRAIL ATR</t>
+          <t>HAZY JOURNEY™ II WATERPROOF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,27 +719,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>przemysl</t>
+          <t>kk_4339471474</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01031646842</t>
+          <t>01037475394</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HAZY JOURNEY™ II WATERPROOF</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -751,22 +751,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4339471474</t>
+          <t>kk_3632271089</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01037475394</t>
+          <t>01035264297</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -783,27 +783,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_3632271089</t>
+          <t>bia5408</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01035264297</t>
+          <t>01037225787</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -815,27 +815,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bia5408</t>
+          <t>kk_4546862086</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01037225787</t>
+          <t>01067901783</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
+          <t>Silver Ridge Elite Convertible Pant</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4546862086</t>
+          <t>shyguy0105</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01067901783</t>
+          <t>01038050293</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Convertible Pant</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,27 +879,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shyguy0105</t>
+          <t>kk_4823936009</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01038050293</t>
+          <t>01089393759</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,12 +911,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4823936009</t>
+          <t>sunnyway21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01089393759</t>
+          <t>01021890517</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>Triple Canyon 24L Backpack</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -943,27 +943,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sunnyway21</t>
+          <t>kk_4581508260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01021890517</t>
+          <t>01089654012</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Triple Canyon 24L Backpack</t>
+          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -975,12 +975,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4581508260</t>
+          <t>jjjino</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01089654012</t>
+          <t>01053807866</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
+          <t>Tumu Heights™ Jacket</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jjjino</t>
+          <t>firstbaek</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01053807866</t>
+          <t>01042145317</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tumu Heights™ Jacket</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,27 +1039,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>firstbaek</t>
+          <t>siwago</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01042145317</t>
+          <t>01033066627</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,27 +1071,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>siwago</t>
+          <t>my8532185</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01033066627</t>
+          <t>01029602185</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>W's Hollowtop Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,12 +1103,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>my8532185</t>
+          <t>zzzing2sj</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01029602185</t>
+          <t>01040825103</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>W's Hollowtop Mountain 2L Jacket</t>
+          <t>JAAWAA WP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zzzing2sj</t>
+          <t>senggun</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01040825103</t>
+          <t>01053217050</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JAAWAA WP</t>
+          <t>Silver Ridge Utility Vest</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,27 +1167,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>senggun</t>
+          <t>umbro98sc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01053217050</t>
+          <t>01027941141</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Silver Ridge Utility Vest</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,27 +1199,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>umbro98sc</t>
+          <t>kk_2958892604</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01027941141</t>
+          <t>01032407670</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,27 +1231,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_2958892604</t>
+          <t>kk_4229942652</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01032407670</t>
+          <t>01074586556</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's Dart Forest Corduroy Shirts</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4229942652</t>
+          <t>rkdwjd1107</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01074586556</t>
+          <t>01086634156</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>M's Dart Forest Corduroy Shirts</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rkdwjd1107</t>
+          <t>kk_4653279631</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01086634156</t>
+          <t>01048492743</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>M's Jerry Cove Crew</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4653279631</t>
+          <t>qwertlhy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01048492743</t>
+          <t>01022573817</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>M's Jerry Cove Crew</t>
+          <t>THRIVE REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwertlhy</t>
+          <t>kk_4824047142</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01022573817</t>
+          <t>01093696318</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>THRIVE REVIVE SHANDAL</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,27 +1391,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4824047142</t>
+          <t>henhaojin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01093696318</t>
+          <t>01053508016</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>M's Current Cove Tapered Pants</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,27 +1423,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>henhaojin</t>
+          <t>yalrud</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01053508016</t>
+          <t>01093710427</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>M's Current Cove Tapered Pants</t>
+          <t>VOYAGER FLX PCT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,27 +1455,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yalrud</t>
+          <t>kk_4742727612</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01093710427</t>
+          <t>01048438355</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VOYAGER FLX PCT</t>
+          <t>Pepper Rock 23L Backpack</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,27 +1487,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4742727612</t>
+          <t>kk_4811115248</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01048438355</t>
+          <t>01032638676</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pepper Rock 23L Backpack</t>
+          <t>M's Second Peak Crew</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4811115248</t>
+          <t>hikehiking</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01032638676</t>
+          <t>01064558877</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>M's Second Peak Crew</t>
+          <t>CRESTWOOD MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hikehiking</t>
+          <t>serejohn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01064558877</t>
+          <t>01062169182</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CRESTWOOD MID WATERPROOF WIDE</t>
+          <t>[GRAFFLEX] Dash to Cove Graphic Tee</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1583,27 +1583,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>serejohn</t>
+          <t>kk_4305828924</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01062169182</t>
+          <t>01052248580</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[GRAFFLEX] Dash to Cove Graphic Tee</t>
+          <t>Castle Rock™ 20L Backpack II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4305828924</t>
+          <t>gamja</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01052248580</t>
+          <t>01076747777</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Castle Rock™ 20L Backpack II</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,12 +1647,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gamja</t>
+          <t>kk_4234884689_2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01076747777</t>
+          <t>01056418131</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>Marble Canyon™ Overlay Hoodie</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,27 +1679,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4234884689_2</t>
+          <t>kk_4640153364</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01056418131</t>
+          <t>01082254246</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marble Canyon™ Overlay Hoodie</t>
+          <t>PFG Unted™ Pant</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4640153364</t>
+          <t>kk_2986632173</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01082254246</t>
+          <t>01094641234</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PFG Unted™ Pant</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1743,22 +1743,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_2986632173</t>
+          <t>kk_3225225310</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01094641234</t>
+          <t>01032977623</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1775,27 +1775,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_3225225310</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01032977623</t>
+          <t>01029767391</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Bonre Forest 20L Packable Backpack</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1807,27 +1807,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4304355753</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01029767391</t>
+          <t>01041289534</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bonre Forest 20L Packable Backpack</t>
+          <t>Crest To Valley Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4304355753</t>
+          <t>ounorman</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01041289534</t>
+          <t>01051592511</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crest To Valley Graphic Ss Tee</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1871,27 +1871,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>montrail</t>
+          <t>boribori123</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01096613534</t>
+          <t>01033660769</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PFG Unted™ Pant</t>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ounorman</t>
+          <t>c300047</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01051592511</t>
+          <t>01032881635</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Acker Rock Twill Short</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1935,12 +1935,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>boribori123</t>
+          <t>c100224</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01033660769</t>
+          <t>01053261660</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>W Saudan Pro 3L Shell</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1967,86 +1967,78 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>c300047</t>
+          <t>jhoh55555</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01032881635</t>
+          <t>01062626688</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Acker Rock Twill Short</t>
-        </is>
-      </c>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>c100224</t>
+          <t>kk_4512211992</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01053261660</t>
+          <t>01040855407</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>W Saudan Pro 3L Shell</t>
-        </is>
-      </c>
+          <t>KAKAO_FridnsTalk_CartSale</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jhoh55555</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01062626688</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2059,12 +2051,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4512211992</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01040855407</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2066,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2087,12 +2079,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2102,7 +2094,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2115,12 +2107,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_3649011176</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01029317964</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2130,35 +2122,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2171,68 +2163,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3649011176</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01029317964</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lscbo76</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01025029158</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2242,7 +2234,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2283,12 +2275,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>somsea</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01028811570</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2298,7 +2290,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2311,68 +2303,68 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2382,7 +2374,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2395,22 +2387,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>somsea</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01028811570</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2423,22 +2415,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>mezzo304</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01032400300</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2451,78 +2443,78 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2535,12 +2527,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2550,7 +2542,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2563,12 +2555,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2578,35 +2570,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2619,12 +2611,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2634,35 +2626,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2675,22 +2667,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2703,22 +2695,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2731,40 +2723,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2774,7 +2766,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2787,12 +2779,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2802,7 +2794,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2815,22 +2807,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2843,40 +2835,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2886,53 +2878,53 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2942,7 +2934,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2983,12 +2975,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2998,7 +2990,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3011,12 +3003,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3026,25 +3018,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3054,7 +3046,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3067,12 +3059,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3082,25 +3074,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3110,25 +3102,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3138,7 +3130,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3151,12 +3143,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3166,7 +3158,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3179,22 +3171,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3207,50 +3199,50 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3263,12 +3255,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3278,7 +3270,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3291,12 +3283,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3306,25 +3298,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3334,25 +3326,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3362,35 +3354,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3403,22 +3395,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3431,22 +3423,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3459,12 +3451,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3474,25 +3466,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3502,25 +3494,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3530,53 +3522,53 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3586,25 +3578,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3614,63 +3606,63 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3683,40 +3675,40 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3739,12 +3731,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3754,35 +3746,35 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3795,12 +3787,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3810,25 +3802,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3838,119 +3830,119 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3963,96 +3955,96 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4062,7 +4054,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4075,12 +4067,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4090,109 +4082,109 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4202,7 +4194,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4215,12 +4207,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4230,63 +4222,63 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -4299,50 +4291,50 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4840510971</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01083115500</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4355,190 +4347,190 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4551,22 +4543,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4579,40 +4571,40 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4622,137 +4614,137 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4762,7 +4754,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4775,134 +4767,134 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4915,50 +4907,50 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>acp1011</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01045809723</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4971,12 +4963,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4986,35 +4978,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5027,50 +5019,50 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5083,236 +5075,236 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5322,7 +5314,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5335,124 +5327,124 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5462,81 +5454,81 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5559,40 +5551,40 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5602,69 +5594,69 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5699,152 +5691,152 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5854,35 +5846,35 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5895,12 +5887,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5910,63 +5902,63 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -5979,68 +5971,68 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6050,119 +6042,119 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -6175,12 +6167,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6196,85 +6188,85 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -6287,22 +6279,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6315,308 +6307,28 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>kk_4351409443</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>01050585646</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>kk_4703272205</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>01062682325</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>LMS_ECOM_0410exclusive2</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>loyed24</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>01085487901</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>LMS_ECOM_0410exclusive2</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>hihijs34</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>01093230529</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>manong0821</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>01036923281</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>LMS_ECOM_0410exclusive2</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr">
-        <is>
           <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>mwnew5</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>01091343604</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>alswjd7015</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>01039137015</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>kk_3837527580</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>01084311738</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>LMS_ECOM_0410exclusive2</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>kk_2750710108</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>01062707475</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>kk_4841861142</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>01052528559</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>6968489536332</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2023,22 +2023,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2051,22 +2051,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2079,56 +2079,56 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_3649011176</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01029317964</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3649011176</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01029317964</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2191,22 +2191,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2219,56 +2219,56 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2331,22 +2331,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2387,12 +2387,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2415,22 +2415,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2471,12 +2471,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2486,25 +2486,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2527,50 +2527,50 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2583,12 +2583,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2598,53 +2598,53 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2667,22 +2667,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2723,68 +2723,68 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2794,25 +2794,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2835,12 +2835,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2863,22 +2863,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2891,40 +2891,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2934,53 +2934,53 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2990,25 +2990,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3031,22 +3031,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3059,40 +3059,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3102,81 +3102,81 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3199,12 +3199,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3227,12 +3227,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3242,81 +3242,81 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3326,35 +3326,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3367,12 +3367,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3382,25 +3382,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3410,53 +3410,53 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3466,63 +3466,63 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3535,12 +3535,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3550,25 +3550,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3578,25 +3578,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4840510971</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01083115500</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3606,69 +3606,69 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3759,12 +3759,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3815,17 +3815,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3843,78 +3843,78 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3927,78 +3927,78 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4011,56 +4011,56 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4095,68 +4095,68 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4166,25 +4166,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4194,63 +4194,63 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4263,78 +4263,78 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4347,12 +4347,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4362,81 +4362,81 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4459,22 +4459,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4487,12 +4487,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4502,91 +4502,91 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4599,68 +4599,68 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4670,91 +4670,91 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4767,12 +4767,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4795,50 +4795,50 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4851,124 +4851,124 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4841861142</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01052528559</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4978,35 +4978,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5019,68 +5019,68 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5103,78 +5103,78 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5187,12 +5187,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5208,141 +5208,141 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -5355,12 +5355,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5370,35 +5370,35 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>acp1011</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01045809723</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -5411,50 +5411,50 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -5467,40 +5467,40 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5510,193 +5510,193 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5706,137 +5706,137 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4351409443</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01050585646</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5846,25 +5846,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5887,50 +5887,50 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5943,22 +5943,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -5971,22 +5971,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -5999,22 +5999,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6027,96 +6027,96 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6126,25 +6126,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6167,12 +6167,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6182,63 +6182,63 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -6251,22 +6251,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -6279,56 +6279,56 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2067,12 +2067,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_2766947879</t>
+          <t>kk_3297935659</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01040508131</t>
+          <t>01090281747</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2095,12 +2095,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3297935659</t>
+          <t>kk_2766947879</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01090281747</t>
+          <t>01040508131</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2123,12 +2123,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>s09635</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01090472784</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2151,12 +2151,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2207,12 +2207,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4750697279</t>
+          <t>kk_3672780564</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01086127388</t>
+          <t>01089459294</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>kk_4750697279</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01086127388</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,13 +2250,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2291,50 +2291,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4660543031</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01065173006</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_2997012029</t>
+          <t>kk_4819859269</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01028601556</t>
+          <t>01033625849</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2347,22 +2347,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4819859269</t>
+          <t>kk_4819571980</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01033625849</t>
+          <t>01032678993</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2375,12 +2375,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4819571980</t>
+          <t>kk_2997012029</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01032678993</t>
+          <t>01028601556</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2403,68 +2403,68 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4660543031</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01065173006</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>vijkk48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01049214164</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2474,25 +2474,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2515,22 +2515,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4842492680</t>
+          <t>eastehdwk</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01024861808</t>
+          <t>01084434416</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2543,12 +2543,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>vijkk48</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01049214164</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2571,22 +2571,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>eastehdwk</t>
+          <t>kk_4841960111</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01084434416</t>
+          <t>01033587128</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2599,22 +2599,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4224863579</t>
+          <t>kk_4842492680</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01045995157</t>
+          <t>01024861808</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2627,50 +2627,50 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4224863579</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01045995157</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4841960111</t>
+          <t>kk_4833693850</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01033587128</t>
+          <t>01038159698</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2683,68 +2683,68 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4833693850</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01038159698</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4820300458</t>
+          <t>kk_4817183511</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01059188956</t>
+          <t>01038475953</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4819009863</t>
+          <t>b1ue7</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01033396228</t>
+          <t>01088937612</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2810,35 +2810,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4837286516</t>
+          <t>kk_4712682242</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01092741887</t>
+          <t>01089596094</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2851,40 +2851,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_3522681591</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01042232282</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>stopzero</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01090058585</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2894,147 +2894,147 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4817183511</t>
+          <t>kk_3392285660</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01038475953</t>
+          <t>01097678768</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3392285660</t>
+          <t>kk_4837286516</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01097678768</t>
+          <t>01092741887</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3821943032</t>
+          <t>kk_4843239939</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01040419162</t>
+          <t>01025351587</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_3693928814</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01026763178</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3047,50 +3047,50 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4819009863</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01033396228</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3382857459</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01057126210</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3103,12 +3103,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3522681591</t>
+          <t>kk_3821943032</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01042232282</t>
+          <t>01040419162</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3131,12 +3131,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>khj2155</t>
+          <t>kk_4820300458</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01067617228</t>
+          <t>01059188956</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3159,40 +3159,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>swd71</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01071953545</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>stopzero</t>
+          <t>khj2155</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01090058585</t>
+          <t>01067617228</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3208,19 +3208,19 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>swd71</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01071953545</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3236,29 +3236,29 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4843239939</t>
+          <t>kk_3693928814</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01025351587</t>
+          <t>01026763178</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3271,12 +3271,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4712682242</t>
+          <t>kk_3382857459</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01089596094</t>
+          <t>01057126210</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3299,12 +3299,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>b1ue7</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01088937612</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3314,30 +3314,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4826503124</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01089846463</t>
+          <t>01042004564</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3348,35 +3348,35 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4825081949</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01089579189</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3411,22 +3411,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4842951523</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01051558480</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3439,22 +3439,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_4842375919</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01054212093</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3467,22 +3467,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4746257748</t>
+          <t>kk_4653613871</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01047829639</t>
+          <t>01087303425</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3495,50 +3495,50 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_3457131246</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01050362153</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>hero8548</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01092748548</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3551,12 +3551,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3566,35 +3566,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4653613871</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01087303425</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3607,12 +3607,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>jghglg</t>
+          <t>kk_4760874675</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01077584718</t>
+          <t>01092960558</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3635,40 +3635,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4843247304</t>
+          <t>melodyhj</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01091358534</t>
+          <t>01040480010</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hero8548</t>
+          <t>kk_3438127132</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01092748548</t>
+          <t>01042465894</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3678,119 +3678,119 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4443220093</t>
+          <t>kk_4842951523</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01050391223</t>
+          <t>01051558480</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bubhak</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01030100699</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>vtjddn</t>
+          <t>kk_4842927888</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01041346668</t>
+          <t>01038403700</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3803,50 +3803,50 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_4443220093</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01050391223</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4826503124</t>
+          <t>kk_4746257748</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01042004564</t>
+          <t>01047829639</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3859,12 +3859,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>jghglg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01077584718</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3887,68 +3887,68 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>melodyhj</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01040480010</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4842375919</t>
+          <t>kk_4825081949</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01054212093</t>
+          <t>01089579189</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4842927888</t>
+          <t>bubhak</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01038403700</t>
+          <t>01030100699</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3971,40 +3971,40 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4835462666</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01025263630</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_3529523763</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01085373147</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4014,35 +4014,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4760874675</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01092960558</t>
+          <t>01089846463</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4055,40 +4055,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>vtjddn</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01041346668</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kimmk12</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01092235669</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4104,29 +4104,29 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4835462666</t>
+          <t>kimmk12</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01025263630</t>
+          <t>01092235669</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4139,96 +4139,96 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_3529523763</t>
+          <t>kk_4843247304</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01085373147</t>
+          <t>01091358534</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_3438127132</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01042465894</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3457131246</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01050362153</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>yeoks73</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01062816207</t>
+          <t>01039056708</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4244,47 +4244,47 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_3879655601</t>
+          <t>kk_4842703404</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01066650864</t>
+          <t>01027721118</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_4842756928</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01067660130</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4300,57 +4300,57 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kojn3718</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01090473718</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4842257901</t>
+          <t>sunlight97</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01099969825</t>
+          <t>01098067107</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4363,12 +4363,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4842227811</t>
+          <t>kk_4842694517</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01053115045</t>
+          <t>01033999168</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4391,12 +4391,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4419,12 +4419,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4843491166</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01044880321</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4440,7 +4440,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4479679945</t>
+          <t>kk_4842831681</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01091309005</t>
+          <t>01033574114</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4496,47 +4496,47 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mhck94148967</t>
+          <t>kk_3630958119</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01037291432</t>
+          <t>01077413527</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_4842999655</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01080258508</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4552,19 +4552,19 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>newbbaccom</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01039056708</t>
+          <t>01025776082</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4580,159 +4580,159 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4842710536</t>
+          <t>kk_3879655601</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01036878125</t>
+          <t>01066650864</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>newbbaccom</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01025776082</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3139519743</t>
+          <t>kk_4479679945</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01063851075</t>
+          <t>01091309005</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4842422203</t>
+          <t>kk_4843482023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01031681399</t>
+          <t>01030727029</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kiwi3023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01075047415</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4842999655</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01080258508</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4748,19 +4748,19 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>kk_4842224344</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01071616299</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4776,47 +4776,47 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3637355234</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01025659242</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4842184373</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01031320092</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4839,22 +4839,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4843482023</t>
+          <t>bobo10</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01030727029</t>
+          <t>01085251319</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4867,12 +4867,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>syosyol</t>
+          <t>kk_4842405217</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01064885418</t>
+          <t>01040880701</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4888,19 +4888,19 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4842831681</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01033574114</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4916,47 +4916,47 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4842135174</t>
+          <t>kk_3139519743</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01072426633</t>
+          <t>01063851075</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>kk_4842227811</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01053115045</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4979,12 +4979,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4842460884</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01066121103</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5000,19 +5000,19 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4842694517</t>
+          <t>yeoks73</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01033999168</t>
+          <t>01062816207</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5028,75 +5028,75 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kojn3718</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01090473718</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4843491166</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01044880321</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kjyun3070</t>
+          <t>khj426</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01025037487</t>
+          <t>01041416347</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5119,68 +5119,68 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sunlight97</t>
+          <t>jaeyouri</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01098067107</t>
+          <t>01099842856</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>teenglory</t>
+          <t>kk_4842422203</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01028236541</t>
+          <t>01031681399</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>jaeyouri</t>
+          <t>kk_4843002291</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01099842856</t>
+          <t>01024118610</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5190,25 +5190,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>khj426</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01041416347</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5224,29 +5224,29 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_4481598577</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01082947677</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5259,12 +5259,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4843392227</t>
+          <t>jangshin711</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01031802445</t>
+          <t>01062415654</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5287,12 +5287,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3630958119</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01077413527</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5308,19 +5308,19 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>nohya2</t>
+          <t>kk_4842694508</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01020112033</t>
+          <t>01032274987</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5336,75 +5336,75 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4842224344</t>
+          <t>kk_4842950188</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01071616299</t>
+          <t>01054340750</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>kk_4843392227</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01031802445</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kiwi3023</t>
+          <t>whdxo30</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01075047415</t>
+          <t>01098421448</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5420,19 +5420,19 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5448,19 +5448,19 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4842881382</t>
+          <t>kk_4842135174</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01033848857</t>
+          <t>01072426633</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>syosyol</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01064885418</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5504,7 +5504,7 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5539,68 +5539,68 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4843149504</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01056900629</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4842756928</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01067660130</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5616,19 +5616,19 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4842694508</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01032274987</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5644,19 +5644,19 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_4842710536</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01036878125</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5672,47 +5672,47 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4481598577</t>
+          <t>kjyun3070</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01082947677</t>
+          <t>01025037487</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>whdxo30</t>
+          <t>teenglory</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01098421448</t>
+          <t>01028236541</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5735,106 +5735,106 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>mhck94148967</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01037291432</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>bobo10</t>
+          <t>kk_4842881382</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01085251319</t>
+          <t>01033848857</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_3637355234</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01025659242</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4842950188</t>
+          <t>kk_4843149504</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01054340750</t>
+          <t>01056900629</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5847,12 +5847,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>jangshin711</t>
+          <t>kk_4842184373</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01062415654</t>
+          <t>01031320092</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5868,19 +5868,19 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4843002291</t>
+          <t>kk_4842460884</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01024118610</t>
+          <t>01066121103</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5896,19 +5896,19 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5931,12 +5931,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_4842257901</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01099969825</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5952,19 +5952,19 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4842405217</t>
+          <t>nohya2</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01040880701</t>
+          <t>01020112033</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5980,7 +5980,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2067,12 +2067,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_2766947879</t>
+          <t>kk_3297935659</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01040508131</t>
+          <t>01090281747</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2095,12 +2095,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3297935659</t>
+          <t>kk_2766947879</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01090281747</t>
+          <t>01040508131</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2123,12 +2123,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2151,22 +2151,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_4826165723</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01063388703</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2179,22 +2179,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4826165723</t>
+          <t>s09635</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01063388703</t>
+          <t>01090472784</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2207,12 +2207,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>kk_4750697279</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01086127388</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4750697279</t>
+          <t>kk_3672780564</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01086127388</t>
+          <t>01089459294</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,119 +2250,119 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4819859269</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01033625849</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4660543031</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01065173006</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4660543031</t>
+          <t>kk_4819571980</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01065173006</t>
+          <t>01032678993</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_3328286087</t>
+          <t>kk_2997012029</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01098090201</t>
+          <t>01028601556</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2375,22 +2375,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_2997012029</t>
+          <t>kk_3328286087</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01028601556</t>
+          <t>01098090201</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2403,22 +2403,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4819571980</t>
+          <t>kk_4819859269</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01032678993</t>
+          <t>01033625849</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2431,12 +2431,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_4833693850</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01038159698</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2446,63 +2446,63 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vijkk48</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01049214164</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4842492680</t>
+          <t>eastehdwk</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01024861808</t>
+          <t>01084434416</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2515,12 +2515,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4224863579</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01045995157</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2543,40 +2543,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4841960111</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01033587128</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_4224863579</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01045995157</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2599,12 +2599,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2614,53 +2614,53 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4841960111</t>
+          <t>kk_4842492680</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01033587128</t>
+          <t>01024861808</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2683,12 +2683,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>eastehdwk</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01084434416</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2711,22 +2711,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4833693850</t>
+          <t>vijkk48</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01038159698</t>
+          <t>01049214164</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2739,50 +2739,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4819009863</t>
+          <t>kk_4820300458</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01033396228</t>
+          <t>01059188956</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2795,12 +2795,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>b1ue7</t>
+          <t>kk_4843239939</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01088937612</t>
+          <t>01025351587</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2810,63 +2810,63 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4820300458</t>
+          <t>kk_4817183511</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01059188956</t>
+          <t>01038475953</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2879,40 +2879,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>swd71</t>
+          <t>kk_4712682242</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01071953545</t>
+          <t>01089596094</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4819009863</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01033396228</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2928,29 +2928,29 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_3693928814</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01026763178</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2963,40 +2963,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_3821943032</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01040419162</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>khj2155</t>
+          <t>kk_3693928814</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01067617228</t>
+          <t>01026763178</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3006,53 +3006,53 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4837286516</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01092741887</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>stopzero</t>
+          <t>kk_3522681591</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01090058585</t>
+          <t>01042232282</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3062,25 +3062,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3392285660</t>
+          <t>kk_3382857459</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01097678768</t>
+          <t>01057126210</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3090,53 +3090,53 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4843239939</t>
+          <t>kk_3392285660</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01025351587</t>
+          <t>01097678768</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_3382857459</t>
+          <t>stopzero</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01057126210</t>
+          <t>01090058585</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3159,50 +3159,50 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4712682242</t>
+          <t>b1ue7</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01089596094</t>
+          <t>01088937612</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4817183511</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01038475953</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3215,96 +3215,96 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3522681591</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01042232282</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>swd71</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01071953545</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4837286516</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01092741887</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_3821943032</t>
+          <t>khj2155</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01040419162</t>
+          <t>01067617228</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_3457131246</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01050362153</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3342,35 +3342,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>vtjddn</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01041346668</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3383,50 +3383,50 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bubhak</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01030100699</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4842951523</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01051558480</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3439,106 +3439,106 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4825081949</t>
+          <t>kk_4843247304</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01089579189</t>
+          <t>01091358534</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kk_3438127132</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01042465894</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_4443220093</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01050391223</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kimmk12</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01092235669</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3551,106 +3551,106 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4842375919</t>
+          <t>kk_4825081949</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01054212093</t>
+          <t>01089579189</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>melodyhj</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01040480010</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_3457131246</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01050362153</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4826503124</t>
+          <t>kk_4842375919</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01042004564</t>
+          <t>01054212093</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3663,12 +3663,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3678,25 +3678,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kimmk12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01092235669</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3712,29 +3712,29 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4842951523</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01051558480</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3747,22 +3747,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4842275089</t>
+          <t>vtjddn</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01033934089</t>
+          <t>01041346668</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3775,22 +3775,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4746257748</t>
+          <t>kk_4842275089</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01047829639</t>
+          <t>01033934089</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3803,56 +3803,56 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>hero8548</t>
+          <t>melodyhj</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01092748548</t>
+          <t>01040480010</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3438127132</t>
+          <t>kk_4653613871</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01042465894</t>
+          <t>01087303425</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3887,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_3529523763</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01085373147</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3902,35 +3902,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3529523763</t>
+          <t>kk_4826503124</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01085373147</t>
+          <t>01042004564</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3943,50 +3943,50 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4653613871</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01087303425</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4843247304</t>
+          <t>jghglg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01091358534</t>
+          <t>01077584718</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3999,22 +3999,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>jghglg</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01077584718</t>
+          <t>01089846463</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4027,40 +4027,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>bubhak</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01089846463</t>
+          <t>01030100699</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4835462666</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01025263630</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4070,25 +4070,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4443220093</t>
+          <t>kk_4746257748</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01050391223</t>
+          <t>01047829639</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4098,91 +4098,91 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_4835462666</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01025263630</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>hero8548</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01092748548</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4760874675</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01092960558</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4195,12 +4195,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_4760874675</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01092960558</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4210,91 +4210,91 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4842257901</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01099969825</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sunlight97</t>
+          <t>kk_4842999655</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01098067107</t>
+          <t>01080258508</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4843491166</t>
+          <t>whdxo30</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01044880321</t>
+          <t>01098421448</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -4307,12 +4307,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4842694508</t>
+          <t>yeoks73</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01032274987</t>
+          <t>01062816207</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4335,12 +4335,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hisooyong</t>
+          <t>kojn3718</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01026866117</t>
+          <t>01090473718</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4363,40 +4363,40 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>mhck94148967</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01037291432</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>kk_4843482023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01030727029</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4412,19 +4412,19 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01039056708</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4440,19 +4440,19 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>hisooyong</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01026866117</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4468,19 +4468,19 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>kk_4842460884</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01066121103</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4496,7 +4496,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
@@ -4531,40 +4531,40 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kjyun3070</t>
+          <t>kk_3139519743</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01025037487</t>
+          <t>01063851075</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kk_3630958119</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01077413527</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4580,19 +4580,19 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>teenglory</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01028236541</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4608,47 +4608,47 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>bobo10</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01085251319</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nohya2</t>
+          <t>kk_4842405217</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01020112033</t>
+          <t>01040880701</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4664,19 +4664,19 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4842999655</t>
+          <t>khj426</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01080258508</t>
+          <t>01041416347</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4699,22 +4699,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4842422203</t>
+          <t>kk_4842881382</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01031681399</t>
+          <t>01033848857</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4727,40 +4727,40 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3139519743</t>
+          <t>kk_4479679945</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01063851075</t>
+          <t>01091309005</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4776,19 +4776,19 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4842227811</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01053115045</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4842460884</t>
+          <t>kk_4842257901</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01066121103</t>
+          <t>01099969825</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4832,19 +4832,19 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jaeyouri</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01099842856</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4854,25 +4854,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4842756928</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01067660130</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4888,47 +4888,47 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4481598577</t>
+          <t>kjyun3070</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01082947677</t>
+          <t>01025037487</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4843002291</t>
+          <t>kk_4842227811</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01024118610</t>
+          <t>01053115045</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4944,47 +4944,47 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4842135174</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01072426633</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4843482023</t>
+          <t>newbbaccom</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01030727029</t>
+          <t>01025776082</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5007,12 +5007,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_4842224344</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01071616299</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5028,19 +5028,19 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3630958119</t>
+          <t>jangshin711</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01077413527</t>
+          <t>01062415654</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5056,19 +5056,19 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4842710536</t>
+          <t>kk_4842694508</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01036878125</t>
+          <t>01032274987</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5084,29 +5084,29 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5119,12 +5119,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4842224344</t>
+          <t>nohya2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01071616299</t>
+          <t>01020112033</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5140,47 +5140,47 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>mhck94148967</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01037291432</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kiwi3023</t>
+          <t>kk_4842184373</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01075047415</t>
+          <t>01031320092</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5196,19 +5196,19 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4842881382</t>
+          <t>kk_4842135174</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01033848857</t>
+          <t>01072426633</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5231,40 +5231,40 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3637355234</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01025659242</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kiwi3023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01075047415</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5280,19 +5280,19 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4843149504</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01056900629</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5302,25 +5302,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4842756928</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01067660130</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5336,19 +5336,19 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5364,47 +5364,47 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_4842422203</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01031681399</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>newbbaccom</t>
+          <t>teenglory</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01025776082</t>
+          <t>01028236541</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5427,12 +5427,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4842831681</t>
+          <t>jaeyouri</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01033574114</t>
+          <t>01099842856</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5442,25 +5442,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4842694517</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01033999168</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5476,47 +5476,47 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_3879655601</t>
+          <t>kk_4842831681</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01066650864</t>
+          <t>01033574114</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>khj426</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01041416347</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5532,85 +5532,85 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>bobo10</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01085251319</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4842405217</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01040880701</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>syosyol</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01064885418</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -5623,68 +5623,68 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4479679945</t>
+          <t>kk_4481598577</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01091309005</t>
+          <t>01082947677</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>yeoks73</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01062816207</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>syosyol</t>
+          <t>kk_4843002291</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01064885418</t>
+          <t>01024118610</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5700,75 +5700,75 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4842950188</t>
+          <t>kk_4843491166</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01054340750</t>
+          <t>01044880321</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_3879655601</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01039056708</t>
+          <t>01066650864</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4842184373</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01031320092</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5784,47 +5784,47 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>sunlight97</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01098067107</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>jangshin711</t>
+          <t>kk_4842694517</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01062415654</t>
+          <t>01033999168</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5847,12 +5847,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_3637355234</t>
+          <t>kk_4842950188</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01025659242</t>
+          <t>01054340750</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5868,19 +5868,19 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>whdxo30</t>
+          <t>kk_4843149504</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01098421448</t>
+          <t>01056900629</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5890,25 +5890,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>kk_4842703404</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01027721118</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kojn3718</t>
+          <t>kk_4842710536</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01090473718</t>
+          <t>01036878125</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5980,7 +5980,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -2151,22 +2151,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4826165723</t>
+          <t>s09635</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01063388703</t>
+          <t>01090472784</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2179,22 +2179,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>kk_4826165723</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01063388703</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2263,78 +2263,78 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4819859269</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01033625849</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4660543031</t>
+          <t>kk_4819571980</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01065173006</t>
+          <t>01032678993</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4819571980</t>
+          <t>kk_3328286087</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01032678993</t>
+          <t>01098090201</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2347,40 +2347,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_2997012029</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01028601556</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3328286087</t>
+          <t>kk_4660543031</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01098090201</t>
+          <t>01065173006</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2390,35 +2390,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4819859269</t>
+          <t>kk_2997012029</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01033625849</t>
+          <t>01028601556</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2431,22 +2431,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4833693850</t>
+          <t>kk_4842492680</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01038159698</t>
+          <t>01024861808</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2459,12 +2459,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2474,35 +2474,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>eastehdwk</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01084434416</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2515,12 +2515,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2543,40 +2543,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4841960111</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01033587128</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4224863579</t>
+          <t>kk_4833693850</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01045995157</t>
+          <t>01038159698</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2599,78 +2599,78 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4224863579</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01045995157</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4842492680</t>
+          <t>vijkk48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01024861808</t>
+          <t>01049214164</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2683,22 +2683,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841960111</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01033587128</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2711,40 +2711,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>vijkk48</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01049214164</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>eastehdwk</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01084434416</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2760,29 +2760,29 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4820300458</t>
+          <t>swd71</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01059188956</t>
+          <t>01071953545</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2795,50 +2795,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4843239939</t>
+          <t>kk_4820300458</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01025351587</t>
+          <t>01059188956</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4817183511</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01038475953</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2851,40 +2851,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_3392285660</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01097678768</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4712682242</t>
+          <t>kk_3522681591</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01089596094</t>
+          <t>01042232282</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2894,63 +2894,63 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4819009863</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01033396228</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_3693928814</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01026763178</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2963,12 +2963,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3821943032</t>
+          <t>kk_4712682242</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01040419162</t>
+          <t>01089596094</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2978,119 +2978,119 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3693928814</t>
+          <t>b1ue7</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01026763178</t>
+          <t>01088937612</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4837286516</t>
+          <t>khj2155</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01092741887</t>
+          <t>01067617228</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3522681591</t>
+          <t>kk_4837286516</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01042232282</t>
+          <t>01092741887</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3382857459</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01057126210</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3103,12 +3103,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3392285660</t>
+          <t>kk_3382857459</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01097678768</t>
+          <t>01057126210</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3118,35 +3118,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>stopzero</t>
+          <t>kk_4843239939</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01090058585</t>
+          <t>01025351587</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3159,12 +3159,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>b1ue7</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01088937612</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3174,119 +3174,119 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_3821943032</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01040419162</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>swd71</t>
+          <t>stopzero</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01071953545</t>
+          <t>01090058585</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4819009863</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01033396228</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3299,40 +3299,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>khj2155</t>
+          <t>kk_4817183511</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01067617228</t>
+          <t>01038475953</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01089846463</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3342,25 +3342,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_4835462666</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01025263630</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3383,162 +3383,162 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_4843247304</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01091358534</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4842951523</t>
+          <t>kk_3457131246</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01051558480</t>
+          <t>01050362153</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4843247304</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01091358534</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_3438127132</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01042465894</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4443220093</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01050391223</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>bubhak</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01030100699</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3551,50 +3551,50 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4825081949</t>
+          <t>kk_4842275089</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01089579189</t>
+          <t>01033934089</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kimmk12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01092235669</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3607,78 +3607,78 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3457131246</t>
+          <t>kk_4653613871</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01050362153</t>
+          <t>01087303425</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4842375919</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01054212093</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>hero8548</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01092748548</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3691,22 +3691,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kimmk12</t>
+          <t>kk_4826503124</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01092235669</t>
+          <t>01042004564</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3719,22 +3719,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>vtjddn</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01041346668</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3747,134 +3747,134 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>vtjddn</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01041346668</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4842275089</t>
+          <t>kk_4760874675</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01033934089</t>
+          <t>01092960558</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>melodyhj</t>
+          <t>kk_3529523763</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01040480010</t>
+          <t>01085373147</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4653613871</t>
+          <t>kk_3438127132</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01087303425</t>
+          <t>01042465894</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4842927888</t>
+          <t>kk_4746257748</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01038403700</t>
+          <t>01047829639</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3887,22 +3887,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3529523763</t>
+          <t>kk_4842951523</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01085373147</t>
+          <t>01051558480</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3915,12 +3915,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4826503124</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01042004564</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3943,50 +3943,50 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4443220093</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01050391223</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>jghglg</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01077584718</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3999,106 +3999,106 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01089846463</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>bubhak</t>
+          <t>jghglg</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01030100699</t>
+          <t>01077584718</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>kk_4825081949</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01089579189</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4746257748</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01047829639</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4111,22 +4111,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4835462666</t>
+          <t>kk_4842375919</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01025263630</t>
+          <t>01054212093</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4139,68 +4139,68 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>hero8548</t>
+          <t>melodyhj</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01092748548</t>
+          <t>01040480010</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_4842927888</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01038403700</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4760874675</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01092960558</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -4223,40 +4223,40 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4842257901</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01099969825</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4842999655</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01080258508</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4272,19 +4272,19 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>whdxo30</t>
+          <t>kiwi3023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01098421448</t>
+          <t>01075047415</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4300,19 +4300,19 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>yeoks73</t>
+          <t>kk_4842703404</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01062816207</t>
+          <t>01027721118</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4328,19 +4328,19 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kojn3718</t>
+          <t>yeoks73</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01090473718</t>
+          <t>01062816207</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4363,40 +4363,40 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mhck94148967</t>
+          <t>kk_3630958119</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01037291432</t>
+          <t>01077413527</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4843482023</t>
+          <t>jangshin711</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01030727029</t>
+          <t>01062415654</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4412,7 +4412,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4447,12 +4447,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>hisooyong</t>
+          <t>kk_4843149504</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01026866117</t>
+          <t>01056900629</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4462,25 +4462,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4842460884</t>
+          <t>hisooyong</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01066121103</t>
+          <t>01026866117</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4496,19 +4496,19 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_4842227811</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01053115045</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4524,47 +4524,47 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_3139519743</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01063851075</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3630958119</t>
+          <t>khj426</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01077413527</t>
+          <t>01041416347</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4580,29 +4580,29 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_4481598577</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01082947677</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4615,12 +4615,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>bobo10</t>
+          <t>kk_4842950188</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01085251319</t>
+          <t>01054340750</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4636,19 +4636,19 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4842405217</t>
+          <t>kk_4479679945</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01040880701</t>
+          <t>01091309005</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4664,19 +4664,19 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>khj426</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01041416347</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4699,40 +4699,40 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4842881382</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01033848857</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4479679945</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01091309005</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4748,47 +4748,47 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>bobo10</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01085251319</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4842694508</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032274987</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4804,19 +4804,19 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4842257901</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01099969825</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4832,19 +4832,19 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kk_4842405217</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01040880701</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4860,19 +4860,19 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>nohya2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01020112033</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4895,12 +4895,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kjyun3070</t>
+          <t>kk_4842694517</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01025037487</t>
+          <t>01033999168</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4923,12 +4923,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4842227811</t>
+          <t>kk_4842224344</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01053115045</t>
+          <t>01071616299</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4944,57 +4944,57 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_4843392227</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01031802445</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>newbbaccom</t>
+          <t>sunlight97</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01025776082</t>
+          <t>01098067107</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5007,12 +5007,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4842224344</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01071616299</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5028,19 +5028,19 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>jangshin711</t>
+          <t>jaeyouri</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01062415654</t>
+          <t>01099842856</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5050,25 +5050,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4842694508</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01032274987</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5084,19 +5084,19 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_4843002291</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01024118610</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5112,19 +5112,19 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>nohya2</t>
+          <t>kk_4842831681</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01020112033</t>
+          <t>01033574114</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5140,47 +5140,47 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>kk_3637355234</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01025659242</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4842184373</t>
+          <t>teenglory</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01031320092</t>
+          <t>01028236541</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5196,75 +5196,75 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4842135174</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01072426633</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_3637355234</t>
+          <t>mhck94148967</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01025659242</t>
+          <t>01037291432</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kiwi3023</t>
+          <t>syosyol</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01075047415</t>
+          <t>01064885418</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5280,19 +5280,19 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>kk_4842881382</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01033848857</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5308,19 +5308,19 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4842756928</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01067660130</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5336,75 +5336,75 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_3879655601</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01066650864</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4842422203</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01031681399</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>teenglory</t>
+          <t>kk_4842460884</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01028236541</t>
+          <t>01066121103</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5420,19 +5420,19 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>jaeyouri</t>
+          <t>kojn3718</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01099842856</t>
+          <t>01090473718</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5442,25 +5442,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_4842999655</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01080258508</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5476,75 +5476,75 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4842831681</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01033574114</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4843491166</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01044880321</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5560,47 +5560,47 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_4842756928</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01067660130</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>syosyol</t>
+          <t>kk_4842184373</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01064885418</t>
+          <t>01031320092</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5616,47 +5616,47 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4481598577</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01082947677</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5679,12 +5679,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4843002291</t>
+          <t>kjyun3070</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01024118610</t>
+          <t>01025037487</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5700,75 +5700,75 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4843491166</t>
+          <t>kk_4842710536</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01044880321</t>
+          <t>01036878125</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_3879655601</t>
+          <t>kk_3139519743</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01066650864</t>
+          <t>01063851075</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_4842135174</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01072426633</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5784,29 +5784,29 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>sunlight97</t>
+          <t>whdxo30</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01098067107</t>
+          <t>01098421448</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -5819,12 +5819,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4842694517</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01033999168</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5840,57 +5840,57 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4842950188</t>
+          <t>kk_4843482023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01054340750</t>
+          <t>01030727029</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4843149504</t>
+          <t>kk_4842422203</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01056900629</t>
+          <t>01031681399</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -5903,12 +5903,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5924,19 +5924,19 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_4843392227</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01031802445</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5952,19 +5952,19 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4842710536</t>
+          <t>newbbaccom</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01036878125</t>
+          <t>01025776082</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5980,7 +5980,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_segments.xlsx
@@ -1983,22 +1983,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2011,22 +2011,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>greom73</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01086372526</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2067,12 +2067,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_3297935659</t>
+          <t>kk_2766947879</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01090281747</t>
+          <t>01040508131</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2095,12 +2095,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_2766947879</t>
+          <t>kk_3297935659</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01040508131</t>
+          <t>01090281747</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2123,12 +2123,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>s09635</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01090472784</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2151,22 +2151,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>kk_4826165723</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01063388703</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2179,22 +2179,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4826165723</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01063388703</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2263,22 +2263,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4819859269</t>
+          <t>kk_4819571980</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01033625849</t>
+          <t>01032678993</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2291,12 +2291,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4819571980</t>
+          <t>kk_2997012029</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01032678993</t>
+          <t>01028601556</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2347,134 +2347,134 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4660543031</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01065173006</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4660543031</t>
+          <t>kk_4819859269</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01065173006</t>
+          <t>01033625849</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_2997012029</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01028601556</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4842492680</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01024861808</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2487,12 +2487,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2502,35 +2502,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841960111</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01033587128</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2543,40 +2543,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4833693850</t>
+          <t>kk_4224863579</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01038159698</t>
+          <t>01045995157</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2599,12 +2599,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2614,35 +2614,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4224863579</t>
+          <t>vijkk48</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01045995157</t>
+          <t>01049214164</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2655,22 +2655,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>vijkk48</t>
+          <t>kk_4842492680</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01049214164</t>
+          <t>01024861808</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2683,40 +2683,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4841960111</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01033587128</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>eastehdwk</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01084434416</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2732,19 +2732,19 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>eastehdwk</t>
+          <t>kk_4833693850</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01084434416</t>
+          <t>01038159698</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2767,22 +2767,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>swd71</t>
+          <t>kk_3392285660</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01071953545</t>
+          <t>01097678768</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2795,12 +2795,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4820300458</t>
+          <t>kk_3821943032</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01059188956</t>
+          <t>01040419162</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2823,22 +2823,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>stopzero</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01090058585</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2851,12 +2851,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_3392285660</t>
+          <t>kk_3522681591</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01097678768</t>
+          <t>01042232282</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2879,50 +2879,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3522681591</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01042232282</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_3382857459</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01057126210</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2935,22 +2935,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_3693928814</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01026763178</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2963,12 +2963,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4712682242</t>
+          <t>kk_3693928814</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01089596094</t>
+          <t>01026763178</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2991,12 +2991,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>b1ue7</t>
+          <t>kk_4843239939</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01088937612</t>
+          <t>01025351587</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3006,25 +3006,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>khj2155</t>
+          <t>kk_4712682242</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01067617228</t>
+          <t>01089596094</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3034,63 +3034,63 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4837286516</t>
+          <t>b1ue7</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01092741887</t>
+          <t>01088937612</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3103,12 +3103,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3382857459</t>
+          <t>khj2155</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01057126210</t>
+          <t>01067617228</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3118,35 +3118,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4843239939</t>
+          <t>kk_4837286516</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01025351587</t>
+          <t>01092741887</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3159,12 +3159,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4819009863</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01033396228</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3180,47 +3180,47 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_3821943032</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01040419162</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4820300458</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01059188956</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3243,12 +3243,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>stopzero</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01090058585</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3258,81 +3258,81 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4819009863</t>
+          <t>kk_4817183511</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01033396228</t>
+          <t>01038475953</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4817183511</t>
+          <t>swd71</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01038475953</t>
+          <t>01071953545</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>hero8548</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01089846463</t>
+          <t>01092748548</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3342,35 +3342,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4835462666</t>
+          <t>vtjddn</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01025263630</t>
+          <t>01041346668</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3383,50 +3383,50 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4843247304</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01091358534</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3457131246</t>
+          <t>kk_4843247304</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01050362153</t>
+          <t>01091358534</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3439,22 +3439,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kimmk12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01092235669</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3467,50 +3467,50 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_3529523763</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01085373147</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3523,28 +3523,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>bubhak</t>
+          <t>melodyhj</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01030100699</t>
+          <t>01040480010</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kimmk12</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01092235669</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3594,25 +3594,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4653613871</t>
+          <t>kk_4842951523</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01087303425</t>
+          <t>01051558480</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3635,50 +3635,50 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hero8548</t>
+          <t>bubhak</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01092748548</t>
+          <t>01030100699</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3691,12 +3691,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4826503124</t>
+          <t>kk_4760874675</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01042004564</t>
+          <t>01092960558</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3706,91 +3706,91 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>vtjddn</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01041346668</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4746257748</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01047829639</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4760874675</t>
+          <t>kk_3457131246</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01092960558</t>
+          <t>01050362153</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3803,22 +3803,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3529523763</t>
+          <t>kk_4842927888</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01085373147</t>
+          <t>01038403700</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3831,40 +3831,40 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3438127132</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01042465894</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4746257748</t>
+          <t>kk_4443220093</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01047829639</t>
+          <t>01050391223</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3874,63 +3874,63 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4842951523</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01051558480</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_4842375919</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01054212093</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3943,68 +3943,68 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4443220093</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01050391223</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_4825081949</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01089579189</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>jghglg</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01077584718</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4014,30 +4014,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>jghglg</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01077584718</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4048,131 +4048,131 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4825081949</t>
+          <t>kk_4826503124</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01089579189</t>
+          <t>01042004564</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4842375919</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01054212093</t>
+          <t>01089846463</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>melodyhj</t>
+          <t>kk_3438127132</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01040480010</t>
+          <t>01042465894</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4842927888</t>
+          <t>kk_4653613871</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01038403700</t>
+          <t>01087303425</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4195,12 +4195,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>kk_4835462666</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01025263630</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4210,25 +4210,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4842257901</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01099969825</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4244,19 +4244,19 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>syosyol</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01064885418</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4279,12 +4279,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kiwi3023</t>
+          <t>jangshin711</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01075047415</t>
+          <t>01062415654</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4307,50 +4307,50 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>kk_3139519743</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01063851075</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>yeoks73</t>
+          <t>bobo10</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01062816207